--- a/input/marktdaten_weichenantriebe.xlsx
+++ b/input/marktdaten_weichenantriebe.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technologische Trends" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wettbewerb – Umsatz nach Region" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marktanteile Europa (Schätzung)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marktanteile Europa" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,10 +31,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="4">
@@ -81,10 +77,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -92,7 +88,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,10 +453,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
@@ -492,7 +487,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Condition Monitoring / Predictive Maintenance</t>
+          <t>Condition Monitoring &amp; Predictive Maintenance</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -508,7 +503,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Digitale Stellwerksintegration (EULYNX)</t>
+          <t>Digitale Stellwerks- integration (EULYNX)</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -556,7 +551,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Remote Diagnostics &amp; Cloud-Integration</t>
+          <t>Remote Diagnostics &amp; Cloud (Railigent X)</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -567,13 +562,6 @@
       </c>
       <c r="D6" s="2" t="n">
         <v>2.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Power BI: Scatter/Bubble-Chart – X=Reifegrad, Y=Relevanz, Größe=Marktpotenzial</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -587,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -835,13 +823,6 @@
       </c>
       <c r="C16" s="2" t="n">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Power BI: Gruppiertes Balkendiagramm – X=Region, Y=Umsatz, Legende=Unternehmen</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -855,11 +836,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -870,7 +851,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Marktanteil % (Weichenantriebe Europa, Schätzung)</t>
+          <t>Marktanteil % (Schätzung Europa)</t>
         </is>
       </c>
     </row>
@@ -932,13 +913,6 @@
       </c>
       <c r="B7" s="3" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Power BI: Donut-Diagramm – Marktanteile nach Unternehmen</t>
-        </is>
       </c>
     </row>
   </sheetData>
